--- a/cnn results/cnn result.xlsx
+++ b/cnn results/cnn result.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\cnn results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895A3241-2FAF-447E-80BA-D8893990B2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801516EC-A020-4718-8824-9CCB064796A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="time" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="time" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
   <si>
     <t>sigma</t>
   </si>
@@ -98,6 +99,66 @@
   </si>
   <si>
     <t>15763 opacus_udata_cnn_dp_three_stage_summary_sigma2_00_20260110_202933.csv​</t>
+  </si>
+  <si>
+    <t>Run ID / Description</t>
+  </si>
+  <si>
+    <t>Dataset (train / val / test)</t>
+  </si>
+  <si>
+    <t>Sigma (noise multiplier)</t>
+  </si>
+  <si>
+    <t>Target ε</t>
+  </si>
+  <si>
+    <t>Final ε</t>
+  </si>
+  <si>
+    <t>Classification F1 (macro)</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>MAE delayed (min)</t>
+  </si>
+  <si>
+    <t>MAE non-delayed (min)</t>
+  </si>
+  <si>
+    <t>MAE overall (min)</t>
+  </si>
+  <si>
+    <t>csv summary (three-stage, large cdata)</t>
+  </si>
+  <si>
+    <t>55,218 / 7,871 / 15,763</t>
+  </si>
+  <si>
+    <t>1.00 (from filename)</t>
+  </si>
+  <si>
+    <t>run 20260110-19:39:46 (cdatasigma0.50)</t>
+  </si>
+  <si>
+    <t>19,207 / 2,727 / 5,474</t>
+  </si>
+  <si>
+    <t>run 20260110-19:42:23 (cdatasigma0.50, repeat)</t>
+  </si>
+  <si>
+    <t>run 20260110-19:39:58 (cdatasigma1.00)</t>
+  </si>
+  <si>
+    <t>opacus udata</t>
+  </si>
+  <si>
+    <t>non opacus udata</t>
+  </si>
+  <si>
+    <t>cdata opacus</t>
   </si>
 </sst>
 </file>
@@ -146,7 +207,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -169,11 +230,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -185,6 +266,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -467,14 +557,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
     <col min="8" max="14" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,8 +592,11 @@
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -532,7 +625,7 @@
         <v>0.95138285007312295</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -561,136 +654,304 @@
         <v>0.50164456508782196</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:14" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3.0579999999999998</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.71589999999999998</v>
+      </c>
+      <c r="H12" s="2">
+        <v>8.4255999999999993</v>
+      </c>
+      <c r="I12" s="2">
+        <v>4.8490000000000002</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5.7145000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="2">
+        <v>11</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2.9449999999999998</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.54359999999999997</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.71360000000000001</v>
+      </c>
+      <c r="H13" s="2">
+        <v>8.4669000000000008</v>
+      </c>
+      <c r="I13" s="2">
+        <v>4.7637</v>
+      </c>
+      <c r="J13" s="2">
+        <v>5.6597999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6">
+        <f>AVERAGE(C12:C13)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="6">
+        <f>AVERAGE(D12:D13)</f>
+        <v>11</v>
+      </c>
+      <c r="E14" s="6">
+        <f>AVERAGE(E12:E13)</f>
+        <v>3.0015000000000001</v>
+      </c>
+      <c r="F14" s="6">
+        <f>AVERAGE(F12:F13)</f>
+        <v>0.54479999999999995</v>
+      </c>
+      <c r="G14" s="6">
+        <f>AVERAGE(G12:G13)</f>
+        <v>0.71475</v>
+      </c>
+      <c r="H14" s="6">
+        <f>AVERAGE(H12:H13)</f>
+        <v>8.4462499999999991</v>
+      </c>
+      <c r="I14" s="6">
+        <f>AVERAGE(I12:I13)</f>
+        <v>4.8063500000000001</v>
+      </c>
+      <c r="J14" s="6">
+        <f>AVERAGE(J12:J13)</f>
+        <v>5.6871499999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6">
+        <v>11</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.51080000000000003</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0.71840000000000004</v>
+      </c>
+      <c r="H15" s="6">
+        <v>8.8719000000000001</v>
+      </c>
+      <c r="I15" s="6">
+        <v>4.6685999999999996</v>
+      </c>
+      <c r="J15" s="6">
+        <v>5.6856999999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:14" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D71" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F71" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H71" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J71" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M71" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N71" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+    <row r="72" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
         <v>1</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B72" s="2">
         <v>0.44367262209337399</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C72" s="2">
         <v>1.46259770652995E-2</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D72" s="2">
         <v>2.82764220013264E-2</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E72" s="2">
         <v>0.81599541421592303</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F72" s="2">
         <v>12.310812756096301</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G72" s="2">
         <v>14.577960783877099</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H72" s="2">
         <v>0.95138285007312295</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I72" s="2">
         <v>1.45057793488848</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J72" s="2">
         <v>3.03402392662086</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K72" s="2">
         <v>6.37819032139575</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L72" s="2">
         <v>404599</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M72" s="2">
         <v>1802221</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N72" s="2">
         <v>0.12813553514614001</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+    <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
         <v>2</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B73" s="2">
         <v>0.26816671281738003</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C73" s="2">
         <v>1.1342648985602399E-3</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D73" s="2">
         <v>2.2580678749840001E-3</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E73" s="2">
         <v>0.81654416762580695</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F73" s="2">
         <v>13.375944175026399</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G73" s="2">
         <v>15.473525828896999</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H73" s="2">
         <v>0.50164456508782196</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I73" s="2">
         <v>0.99998352736971297</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J73" s="2">
         <v>2.8620222795736101</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K73" s="2">
         <v>6.6868375709511803</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L73" s="2">
         <v>404599</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M73" s="2">
         <v>1802221</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N73" s="2">
         <v>5.3868287199408497E-2</v>
       </c>
     </row>
@@ -701,6 +962,83 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8CC8DD-ACC4-41BB-82CE-4167213D5E66}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:12" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="83.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>101.42</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.36109999999999998</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.63029999999999997</v>
+      </c>
+      <c r="H2" s="2">
+        <v>7.4020000000000001</v>
+      </c>
+      <c r="I2" s="2">
+        <v>3.7728000000000002</v>
+      </c>
+      <c r="J2" s="2">
+        <v>6.2095000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD62EE0-B23C-4003-BB7F-31D7884A295E}">
   <dimension ref="B1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/cnn results/cnn result.xlsx
+++ b/cnn results/cnn result.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\flight delay\stpn paper\STPN-main\cnn results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801516EC-A020-4718-8824-9CCB064796A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEB81DB-29BB-40A8-A619-AB8B5F743B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="time" sheetId="2" r:id="rId3"/>
+    <sheet name="CDATA OPACUS" sheetId="1" r:id="rId1"/>
+    <sheet name="SIMPLE CNN UDATA" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="time" sheetId="2" r:id="rId4"/>
+    <sheet name="UDATA OPACUS" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="91">
   <si>
     <t>sigma</t>
   </si>
@@ -159,13 +161,154 @@
   </si>
   <si>
     <t>cdata opacus</t>
+  </si>
+  <si>
+    <t>arch</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>target_epsilon</t>
+  </si>
+  <si>
+    <t>train_time_seconds</t>
+  </si>
+  <si>
+    <t>train_time_minutes</t>
+  </si>
+  <si>
+    <t>cnn</t>
+  </si>
+  <si>
+    <t>udata</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>15763 cnnopacus_udata_sigma1_00_test_summary_20260111_003829.csv​</t>
+  </si>
+  <si>
+    <t>15763 cnnopacus_udata_sigma2_00_test_summary_20260111_003219.csv​</t>
+  </si>
+  <si>
+    <t>simple_cnn</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>15763 cnnopacus_simple_udata_sigma2_00_train_summary_20260111_051329.csv​</t>
+  </si>
+  <si>
+    <t>15763 cnnopacus_simple_udata_sigma1_00_train_summary_20260111_210902.csv​</t>
+  </si>
+  <si>
+    <t>cdata</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>5474 cnnopacus_cdata_sigma0_00_train_summary_20260111_131412.csv​</t>
+  </si>
+  <si>
+    <t>5474 cnnopacus_cdata_sigma1_00_train_summary_20260111_151301.csv​</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Run / Description</t>
+  </si>
+  <si>
+    <t>Sigma</t>
+  </si>
+  <si>
+    <t>F1 (macro)</t>
+  </si>
+  <si>
+    <t>udata sigma1.00 (test)</t>
+  </si>
+  <si>
+    <t>3.0340 cnnopacus_udata_sigma1_00_test_summary_20260111_003829.csv​</t>
+  </si>
+  <si>
+    <t>udata sigma2.00 (test)</t>
+  </si>
+  <si>
+    <t>2.8620 cnnopacus_udata_sigma2_00_test_summary_20260111_003219.csv​</t>
+  </si>
+  <si>
+    <t>cdata sigma0.00 (train)</t>
+  </si>
+  <si>
+    <t>cdata sigma1.00 (train)</t>
+  </si>
+  <si>
+    <t>cdata sigma0.50 (avg of two runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">udata opacus </t>
+  </si>
+  <si>
+    <t>Run ID (suffix)</t>
+  </si>
+  <si>
+    <t>Ïƒ</t>
+  </si>
+  <si>
+    <t>Final Îµ</t>
+  </si>
+  <si>
+    <t>Cls macro P</t>
+  </si>
+  <si>
+    <t>Cls macro R</t>
+  </si>
+  <si>
+    <t>Cls macro F1</t>
+  </si>
+  <si>
+    <t>Acc</t>
+  </si>
+  <si>
+    <t>MAE delayed &gt;5</t>
+  </si>
+  <si>
+    <t>RMSE delayed &gt;5</t>
+  </si>
+  <si>
+    <t>MAE â‰¤5</t>
+  </si>
+  <si>
+    <t>RMSE â‰¤5</t>
+  </si>
+  <si>
+    <t>MAE overall</t>
+  </si>
+  <si>
+    <t>RMSE overall</t>
+  </si>
+  <si>
+    <t>022124 (run 1, Ïƒ=0.20)</t>
+  </si>
+  <si>
+    <t>024111 (run 2, Ïƒ=0.20)</t>
+  </si>
+  <si>
+    <t>014315 (run 3, Ïƒ=1.50)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +328,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -254,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -277,6 +428,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -292,6 +455,1150 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CDATA OPACUS'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MAE delayed (min)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CDATA OPACUS'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CDATA OPACUS'!$H$2:$H$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>7.6581000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.2805999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.4463000000000008</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.9405000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.450900000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E9FA-44F8-A581-1F453C4559BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CDATA OPACUS'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MAE non-delayed (min)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CDATA OPACUS'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CDATA OPACUS'!$I$2:$I$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5.8148</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.5015999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.8064</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.51</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5727000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E9FA-44F8-A581-1F453C4559BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CDATA OPACUS'!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MAE overall (min)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'CDATA OPACUS'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'CDATA OPACUS'!$J$2:$J$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6.2609000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.4160500000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.6871999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.5821000000000005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.7210999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E9FA-44F8-A581-1F453C4559BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="337480848"/>
+        <c:axId val="337468368"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="337480848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="337468368"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="337468368"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="337480848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>150845</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>270589</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>468086</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9332</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2808EF00-917D-4303-A13C-828D50870164}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -557,411 +1864,1168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
     <col min="8" max="14" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="10">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D2" s="10">
+        <v>15</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.57289999999999996</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.69710000000000005</v>
+      </c>
+      <c r="H2" s="10">
+        <v>7.6581000000000001</v>
+      </c>
+      <c r="I2" s="10">
+        <v>5.8148</v>
+      </c>
+      <c r="J2" s="10">
+        <v>6.2609000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11">
+        <v>291.47749999999996</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0.5665</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.71894999999999998</v>
+      </c>
+      <c r="H3" s="11">
+        <v>8.2805999999999997</v>
+      </c>
+      <c r="I3" s="11">
+        <v>4.5015999999999998</v>
+      </c>
+      <c r="J3" s="11">
+        <v>5.4160500000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="10">
+        <v>11</v>
+      </c>
+      <c r="E4" s="10">
+        <v>3.0015000000000001</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.54479999999999995</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.71479999999999999</v>
+      </c>
+      <c r="H4" s="10">
+        <v>8.4463000000000008</v>
+      </c>
+      <c r="I4" s="10">
+        <v>4.8064</v>
+      </c>
+      <c r="J4" s="10">
+        <v>5.6871999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11">
+        <v>13</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.28744999999999998</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.50605</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.72370000000000001</v>
+      </c>
+      <c r="H5" s="11">
+        <v>8.9405000000000001</v>
+      </c>
+      <c r="I5" s="11">
+        <v>4.51</v>
+      </c>
+      <c r="J5" s="11">
+        <v>5.5821000000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C6" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11">
+        <v>0.219</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0.1434</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.75539999999999996</v>
+      </c>
+      <c r="H6" s="11">
+        <v>11.450900000000001</v>
+      </c>
+      <c r="I6" s="11">
+        <v>2.5727000000000002</v>
+      </c>
+      <c r="J6" s="11">
+        <v>4.7210999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>11</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3.0579999999999998</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.71589999999999998</v>
+      </c>
+      <c r="H16" s="2">
+        <v>8.4255999999999993</v>
+      </c>
+      <c r="I16" s="2">
+        <v>4.8490000000000002</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5.7145000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="2">
+        <v>11</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2.9449999999999998</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.54359999999999997</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.71360000000000001</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8.4669000000000008</v>
+      </c>
+      <c r="I17" s="2">
+        <v>4.7637</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5.6597999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6">
+        <f t="shared" ref="C18:J18" si="0">AVERAGE(C16:C17)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="6">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>3.0015000000000001</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" si="0"/>
+        <v>0.54479999999999995</v>
+      </c>
+      <c r="G18" s="6">
+        <f t="shared" si="0"/>
+        <v>0.71475</v>
+      </c>
+      <c r="H18" s="6">
+        <f t="shared" si="0"/>
+        <v>8.4462499999999991</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>4.8063500000000001</v>
+      </c>
+      <c r="J18" s="6">
+        <f t="shared" si="0"/>
+        <v>5.6871499999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6">
+        <v>11</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.51080000000000003</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0.71840000000000004</v>
+      </c>
+      <c r="H19" s="6">
+        <v>8.8719000000000001</v>
+      </c>
+      <c r="I19" s="6">
+        <v>4.6685999999999996</v>
+      </c>
+      <c r="J19" s="6">
+        <v>5.6856999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>15</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.28989999999999999</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.50129999999999997</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="H20" s="2">
+        <v>9.0091000000000001</v>
+      </c>
+      <c r="I20" s="2">
+        <v>4.3513999999999999</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5.4785000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2">
+        <f t="shared" ref="C21:J21" si="1">AVERAGE(C19:C20)</f>
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="1"/>
+        <v>0.28744999999999998</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="1"/>
+        <v>0.50605</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="1"/>
+        <v>0.72370000000000001</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>8.9405000000000001</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="1"/>
+        <v>4.51</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" si="1"/>
+        <v>5.5821000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="S22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.43448823746586301</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.84283430614755905</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.57293888245186997</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0.69712641578367895</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.6580879165429998</v>
+      </c>
+      <c r="J23" s="2">
+        <v>9.8612681900349894</v>
+      </c>
+      <c r="K23" s="2">
+        <v>5.8148316295339102</v>
+      </c>
+      <c r="L23" s="2">
+        <v>7.2610820726998204</v>
+      </c>
+      <c r="M23" s="2">
+        <v>6.26086665151694</v>
+      </c>
+      <c r="N23" s="2">
+        <v>7.9684797667271798</v>
+      </c>
+      <c r="O23" s="2">
+        <v>132461</v>
+      </c>
+      <c r="P23" s="2">
+        <v>414939</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>15</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="S23" s="2">
+        <v>19207</v>
+      </c>
+      <c r="T23" s="2">
+        <v>2727</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E24" s="2">
+        <v>0.451711130641269</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.56337277787309803</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.50133694505330895</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.72903544026303502</v>
+      </c>
+      <c r="I24" s="2">
+        <v>9.0091117852003304</v>
+      </c>
+      <c r="J24" s="2">
+        <v>11.5548400874446</v>
+      </c>
+      <c r="K24" s="2">
+        <v>4.35137521844376</v>
+      </c>
+      <c r="L24" s="2">
+        <v>5.9354274582352504</v>
+      </c>
+      <c r="M24" s="2">
+        <v>5.4784640810106904</v>
+      </c>
+      <c r="N24" s="2">
+        <v>7.6819604837801796</v>
+      </c>
+      <c r="O24" s="2">
+        <v>132461</v>
+      </c>
+      <c r="P24" s="2">
+        <v>414939</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>15</v>
+      </c>
+      <c r="R24" s="2">
+        <v>0.28990400510647302</v>
+      </c>
+      <c r="S24" s="2">
+        <v>19207</v>
+      </c>
+      <c r="T24" s="2">
+        <v>2727</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s">
+        <v>81</v>
+      </c>
+      <c r="J31" t="s">
+        <v>82</v>
+      </c>
+      <c r="K31" t="s">
+        <v>83</v>
+      </c>
+      <c r="L31" t="s">
+        <v>84</v>
+      </c>
+      <c r="M31" t="s">
+        <v>85</v>
+      </c>
+      <c r="N31" t="s">
+        <v>86</v>
+      </c>
+      <c r="O31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32">
+        <v>0.2</v>
+      </c>
+      <c r="E32">
+        <v>285.28100000000001</v>
+      </c>
+      <c r="F32">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="G32">
+        <v>0.72729999999999995</v>
+      </c>
+      <c r="H32">
+        <v>0.56120000000000003</v>
+      </c>
+      <c r="I32">
+        <v>0.72540000000000004</v>
+      </c>
+      <c r="J32">
+        <v>8.3797999999999995</v>
+      </c>
+      <c r="K32">
+        <v>10.845499999999999</v>
+      </c>
+      <c r="L32">
+        <v>4.4284999999999997</v>
+      </c>
+      <c r="M32">
+        <v>6.0862999999999996</v>
+      </c>
+      <c r="N32">
+        <v>5.3845999999999998</v>
+      </c>
+      <c r="O32">
+        <v>7.5194000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33">
+        <v>0.2</v>
+      </c>
+      <c r="E33">
+        <v>297.67399999999998</v>
+      </c>
+      <c r="F33">
+        <v>0.4466</v>
+      </c>
+      <c r="G33">
+        <v>0.79479999999999995</v>
+      </c>
+      <c r="H33">
+        <v>0.57179999999999997</v>
+      </c>
+      <c r="I33">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="J33">
+        <v>8.1814</v>
+      </c>
+      <c r="K33">
+        <v>10.552199999999999</v>
+      </c>
+      <c r="L33">
+        <v>4.5747</v>
+      </c>
+      <c r="M33">
+        <v>6.3528000000000002</v>
+      </c>
+      <c r="N33">
+        <v>5.4474999999999998</v>
+      </c>
+      <c r="O33">
+        <v>7.5853000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <f>AVERAGE(D32:D33)</f>
+        <v>0.2</v>
+      </c>
+      <c r="E34">
+        <f>AVERAGE(E32:E33)</f>
+        <v>291.47749999999996</v>
+      </c>
+      <c r="F34">
+        <f>AVERAGE(F32:F33)</f>
+        <v>0.45179999999999998</v>
+      </c>
+      <c r="G34">
+        <f>AVERAGE(G32:G33)</f>
+        <v>0.76105</v>
+      </c>
+      <c r="H34">
+        <f>AVERAGE(H32:H33)</f>
+        <v>0.5665</v>
+      </c>
+      <c r="I34">
+        <f>AVERAGE(I32:I33)</f>
+        <v>0.71894999999999998</v>
+      </c>
+      <c r="J34">
+        <f>AVERAGE(J32:J33)</f>
+        <v>8.2805999999999997</v>
+      </c>
+      <c r="K34">
+        <f>AVERAGE(K32:K33)</f>
+        <v>10.69885</v>
+      </c>
+      <c r="L34">
+        <f>AVERAGE(L32:L33)</f>
+        <v>4.5015999999999998</v>
+      </c>
+      <c r="M34">
+        <f>AVERAGE(M32:M33)</f>
+        <v>6.2195499999999999</v>
+      </c>
+      <c r="N34">
+        <f>AVERAGE(N32:N33)</f>
+        <v>5.4160500000000003</v>
+      </c>
+      <c r="O34">
+        <f>AVERAGE(O32:O33)</f>
+        <v>7.5523500000000006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35">
+        <v>1.5</v>
+      </c>
+      <c r="E35">
+        <v>0.219</v>
+      </c>
+      <c r="F35">
+        <v>0.46989999999999998</v>
+      </c>
+      <c r="G35">
+        <v>8.4900000000000003E-2</v>
+      </c>
+      <c r="H35">
+        <v>0.1434</v>
+      </c>
+      <c r="I35">
+        <v>0.75539999999999996</v>
+      </c>
+      <c r="J35">
+        <v>11.450900000000001</v>
+      </c>
+      <c r="K35">
+        <v>14.106400000000001</v>
+      </c>
+      <c r="L35">
+        <v>2.5727000000000002</v>
+      </c>
+      <c r="M35">
+        <v>3.6145999999999998</v>
+      </c>
+      <c r="N35">
+        <v>4.7210999999999999</v>
+      </c>
+      <c r="O35">
+        <v>7.6195000000000004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:15" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="G48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+      <c r="I48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B49" s="2">
+        <v>0.44367262209337399</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1.46259770652995E-2</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2.82764220013264E-2</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.81599541421592303</v>
+      </c>
+      <c r="F49" s="2">
+        <v>12.310812756096301</v>
+      </c>
+      <c r="G49" s="2">
+        <v>14.577960783877099</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0.95138285007312295</v>
+      </c>
+      <c r="I49" s="2">
+        <v>1.45057793488848</v>
+      </c>
+      <c r="J49" s="2">
         <v>3.03402392662086</v>
       </c>
-      <c r="C2" s="2">
+      <c r="K49" s="2">
+        <v>6.37819032139575</v>
+      </c>
+      <c r="L49" s="2">
+        <v>404599</v>
+      </c>
+      <c r="M49" s="2">
+        <v>1802221</v>
+      </c>
+      <c r="N49" s="2">
         <v>0.12813553514614001</v>
       </c>
-      <c r="D2" s="2">
-        <v>0.44367262209337399</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1.46259770652995E-2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2.82764220013264E-2</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.81599541421592303</v>
-      </c>
-      <c r="H2" s="2">
-        <v>12.310812756096301</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.95138285007312295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+    </row>
+    <row r="50" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B50" s="2">
+        <v>0.26816671281738003</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1.1342648985602399E-3</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2.2580678749840001E-3</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.81654416762580695</v>
+      </c>
+      <c r="F50" s="2">
+        <v>13.375944175026399</v>
+      </c>
+      <c r="G50" s="2">
+        <v>15.473525828896999</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0.50164456508782196</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0.99998352736971297</v>
+      </c>
+      <c r="J50" s="2">
         <v>2.8620222795736101</v>
       </c>
-      <c r="C3" s="2">
-        <v>5.3868287199408497E-2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.26816671281738003</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1.1342648985602399E-3</v>
-      </c>
-      <c r="F3" s="2">
-        <v>2.2580678749840001E-3</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.81654416762580695</v>
-      </c>
-      <c r="H3" s="2">
-        <v>13.375944175026399</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.50164456508782196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="2">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2">
-        <v>3.0579999999999998</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.54600000000000004</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0.71589999999999998</v>
-      </c>
-      <c r="H12" s="2">
-        <v>8.4255999999999993</v>
-      </c>
-      <c r="I12" s="2">
-        <v>4.8490000000000002</v>
-      </c>
-      <c r="J12" s="2">
-        <v>5.7145000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="2">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2.9449999999999998</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0.54359999999999997</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.71360000000000001</v>
-      </c>
-      <c r="H13" s="2">
-        <v>8.4669000000000008</v>
-      </c>
-      <c r="I13" s="2">
-        <v>4.7637</v>
-      </c>
-      <c r="J13" s="2">
-        <v>5.6597999999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6">
-        <f>AVERAGE(C12:C13)</f>
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="6">
-        <f>AVERAGE(D12:D13)</f>
-        <v>11</v>
-      </c>
-      <c r="E14" s="6">
-        <f>AVERAGE(E12:E13)</f>
-        <v>3.0015000000000001</v>
-      </c>
-      <c r="F14" s="6">
-        <f>AVERAGE(F12:F13)</f>
-        <v>0.54479999999999995</v>
-      </c>
-      <c r="G14" s="6">
-        <f>AVERAGE(G12:G13)</f>
-        <v>0.71475</v>
-      </c>
-      <c r="H14" s="6">
-        <f>AVERAGE(H12:H13)</f>
-        <v>8.4462499999999991</v>
-      </c>
-      <c r="I14" s="6">
-        <f>AVERAGE(I12:I13)</f>
-        <v>4.8063500000000001</v>
-      </c>
-      <c r="J14" s="6">
-        <f>AVERAGE(J12:J13)</f>
-        <v>5.6871499999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="6">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>11</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.51080000000000003</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.71840000000000004</v>
-      </c>
-      <c r="H15" s="6">
-        <v>8.8719000000000001</v>
-      </c>
-      <c r="I15" s="6">
-        <v>4.6685999999999996</v>
-      </c>
-      <c r="J15" s="6">
-        <v>5.6856999999999998</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:14" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="2">
-        <v>1</v>
-      </c>
-      <c r="B72" s="2">
-        <v>0.44367262209337399</v>
-      </c>
-      <c r="C72" s="2">
-        <v>1.46259770652995E-2</v>
-      </c>
-      <c r="D72" s="2">
-        <v>2.82764220013264E-2</v>
-      </c>
-      <c r="E72" s="2">
-        <v>0.81599541421592303</v>
-      </c>
-      <c r="F72" s="2">
-        <v>12.310812756096301</v>
-      </c>
-      <c r="G72" s="2">
-        <v>14.577960783877099</v>
-      </c>
-      <c r="H72" s="2">
-        <v>0.95138285007312295</v>
-      </c>
-      <c r="I72" s="2">
-        <v>1.45057793488848</v>
-      </c>
-      <c r="J72" s="2">
-        <v>3.03402392662086</v>
-      </c>
-      <c r="K72" s="2">
-        <v>6.37819032139575</v>
-      </c>
-      <c r="L72" s="2">
+      <c r="K50" s="2">
+        <v>6.6868375709511803</v>
+      </c>
+      <c r="L50" s="2">
         <v>404599</v>
       </c>
-      <c r="M72" s="2">
+      <c r="M50" s="2">
         <v>1802221</v>
       </c>
-      <c r="N72" s="2">
-        <v>0.12813553514614001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="2">
-        <v>2</v>
-      </c>
-      <c r="B73" s="2">
-        <v>0.26816671281738003</v>
-      </c>
-      <c r="C73" s="2">
-        <v>1.1342648985602399E-3</v>
-      </c>
-      <c r="D73" s="2">
-        <v>2.2580678749840001E-3</v>
-      </c>
-      <c r="E73" s="2">
-        <v>0.81654416762580695</v>
-      </c>
-      <c r="F73" s="2">
-        <v>13.375944175026399</v>
-      </c>
-      <c r="G73" s="2">
-        <v>15.473525828896999</v>
-      </c>
-      <c r="H73" s="2">
-        <v>0.50164456508782196</v>
-      </c>
-      <c r="I73" s="2">
-        <v>0.99998352736971297</v>
-      </c>
-      <c r="J73" s="2">
-        <v>2.8620222795736101</v>
-      </c>
-      <c r="K73" s="2">
-        <v>6.6868375709511803</v>
-      </c>
-      <c r="L73" s="2">
-        <v>404599</v>
-      </c>
-      <c r="M73" s="2">
-        <v>1802221</v>
-      </c>
-      <c r="N73" s="2">
+      <c r="N50" s="2">
         <v>5.3868287199408497E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29D893EC-4489-4535-9420-D2D268993AF9}">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>13.0274830403055</v>
+      </c>
+      <c r="F2" s="2">
+        <v>15.2098195042417</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.59194196238078201</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1.1517848410009499</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2.87187756410058</v>
+      </c>
+      <c r="J2" s="2">
+        <v>6.5952311055348503</v>
+      </c>
+      <c r="K2" s="2">
+        <v>404599</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1802221</v>
+      </c>
+      <c r="M2" s="2">
+        <v>15</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2.99738144300889E-2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>13827.0564200878</v>
+      </c>
+      <c r="P2" s="2">
+        <v>230.450940334796</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>55218</v>
+      </c>
+      <c r="R2" s="2">
+        <v>7871</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="152.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>12.5845272845339</v>
+      </c>
+      <c r="F3" s="2">
+        <v>14.855511211609</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.70679506345033205</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1.30048600471769</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2.8844618323386899</v>
+      </c>
+      <c r="J3" s="2">
+        <v>6.4685283903450097</v>
+      </c>
+      <c r="K3" s="2">
+        <v>404599</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1802221</v>
+      </c>
+      <c r="M3" s="2">
+        <v>15</v>
+      </c>
+      <c r="N3" s="2">
+        <v>8.5511823460318201E-2</v>
+      </c>
+      <c r="O3" s="2">
+        <v>18617.414036989201</v>
+      </c>
+      <c r="P3" s="2">
+        <v>310.29023394981999</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>55218</v>
+      </c>
+      <c r="R3" s="2">
+        <v>7871</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D8CC8DD-ACC4-41BB-82CE-4167213D5E66}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1038,7 +3102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD62EE0-B23C-4003-BB7F-31D7884A295E}">
   <dimension ref="B1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1136,4 +3200,400 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC616933-7BB7-49D4-8217-210D6D217CF4}">
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:21" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.12809999999999999</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="H2" s="2">
+        <v>12.3108</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.95140000000000002</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="138.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2.3E-3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.8165</v>
+      </c>
+      <c r="H3" s="2">
+        <v>13.3759</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.50160000000000005</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:21" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4">
+        <v>3.03402392662086</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.12813553514614001</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.44367262209337399</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.46259770652995E-2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2.82764220013264E-2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.81599541421592303</v>
+      </c>
+      <c r="H6" s="2">
+        <v>12.310812756096301</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.95138285007312295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2.8620222795736101</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5.3868287199408497E-2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.26816671281738003</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1.1342648985602399E-3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2.2580678749840001E-3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.81654416762580695</v>
+      </c>
+      <c r="H7" s="2">
+        <v>13.375944175026399</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.50164456508782196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:21" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.44367262209337399</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.46259770652995E-2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2.82764220013264E-2</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.81599541421592303</v>
+      </c>
+      <c r="I12" s="2">
+        <v>12.310812756096301</v>
+      </c>
+      <c r="J12" s="2">
+        <v>14.577960783877099</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.95138285007312295</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1.45057793488848</v>
+      </c>
+      <c r="M12" s="2">
+        <v>3.03402392662086</v>
+      </c>
+      <c r="N12" s="2">
+        <v>6.37819032139575</v>
+      </c>
+      <c r="O12" s="2">
+        <v>404599</v>
+      </c>
+      <c r="P12" s="2">
+        <v>1802221</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>15</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0.12813553514614001</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.26816671281738003</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1.1342648985602399E-3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>2.2580678749840001E-3</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.81654416762580695</v>
+      </c>
+      <c r="I13" s="2">
+        <v>13.375944175026399</v>
+      </c>
+      <c r="J13" s="2">
+        <v>15.473525828896999</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.50164456508782196</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.99998352736971297</v>
+      </c>
+      <c r="M13" s="2">
+        <v>2.8620222795736101</v>
+      </c>
+      <c r="N13" s="2">
+        <v>6.6868375709511803</v>
+      </c>
+      <c r="O13" s="2">
+        <v>404599</v>
+      </c>
+      <c r="P13" s="2">
+        <v>1802221</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>15</v>
+      </c>
+      <c r="R13" s="2">
+        <v>5.3868287199408497E-2</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>